--- a/Methodology/PIRNN/03-W-X/Ts-03/Resumo_Estatisticas.xlsx
+++ b/Methodology/PIRNN/03-W-X/Ts-03/Resumo_Estatisticas.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Todos_Modelos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Top_10_Modelos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Top_Modelos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Melhor_Modelo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,16 +474,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.2357513347548522</v>
+        <v>-0.2320325705209549</v>
       </c>
       <c r="D2" t="n">
-        <v>0.771743402764383</v>
+        <v>0.7730435977109311</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1332457885451422</v>
+        <v>0.1328448100806056</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08321379501180241</v>
+        <v>0.08335398947976921</v>
       </c>
     </row>
     <row r="3">
@@ -497,16 +498,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-9.524336947130559</v>
+        <v>-9.352214182673645</v>
       </c>
       <c r="D3" t="n">
-        <v>6.361565598797326</v>
+        <v>6.264953843997129</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8867842069067715</v>
+        <v>0.8722810842933187</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5360276787558561</v>
+        <v>0.5278871394716477</v>
       </c>
     </row>
     <row r="4">
@@ -521,16 +522,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.1104036626052385</v>
+        <v>-0.06479269590637306</v>
       </c>
       <c r="D4" t="n">
-        <v>1.093740056635623</v>
+        <v>1.133062240038725</v>
       </c>
       <c r="E4" t="n">
-        <v>0.106180274424666</v>
+        <v>0.1018188110001874</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1045868482551169</v>
+        <v>0.1083469585333219</v>
       </c>
     </row>
     <row r="5">
@@ -545,16 +546,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.2861613933461771</v>
+        <v>-0.2869184430939266</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8487478990849745</v>
+        <v>0.8530512530212798</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1347390695584036</v>
+        <v>0.1348183785620395</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08891535914853797</v>
+        <v>0.08936618119028013</v>
       </c>
     </row>
     <row r="6">
@@ -569,16 +570,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-9.595967991720393</v>
+        <v>-9.419358591863872</v>
       </c>
       <c r="D6" t="n">
-        <v>6.516294339697076</v>
+        <v>6.415384694681537</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8719762159383858</v>
+        <v>0.857442461560648</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5362467765766838</v>
+        <v>0.5279425979984652</v>
       </c>
     </row>
     <row r="7">
@@ -593,16 +594,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2971707644503388</v>
+        <v>0.3303637120020613</v>
       </c>
       <c r="D7" t="n">
-        <v>1.069974984192442</v>
+        <v>1.095678926147501</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06466336408839854</v>
+        <v>0.06160946771622282</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09844237898584907</v>
+        <v>0.1008072540836347</v>
       </c>
     </row>
   </sheetData>
@@ -663,16 +664,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8494624957867952</v>
+        <v>0.8724239312673273</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07363321681932958</v>
+        <v>0.03800358543695376</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01623181613514933</v>
+        <v>0.01375598261534266</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007939555282902739</v>
+        <v>0.004097764304737041</v>
       </c>
     </row>
     <row r="3">
@@ -687,16 +688,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-7.7939277115241</v>
+        <v>-0.6065233556132513</v>
       </c>
       <c r="D3" t="n">
-        <v>4.342062610044777</v>
+        <v>0.8211386069492407</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7409793367919083</v>
+        <v>0.1353662037752533</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3658636707786069</v>
+        <v>0.06918941801103665</v>
       </c>
     </row>
     <row r="4">
@@ -711,16 +712,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9517905325931304</v>
+        <v>0.9490067402923398</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008820663760407734</v>
+        <v>0.003709638898880805</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004609940196989634</v>
+        <v>0.004876135131672872</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008434594825546472</v>
+        <v>0.0003547272848285044</v>
       </c>
     </row>
     <row r="5">
@@ -735,16 +736,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8824412636470885</v>
+        <v>0.9040985305282276</v>
       </c>
       <c r="D5" t="n">
-        <v>0.063416903326073</v>
+        <v>0.03350612576909103</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01231552652458572</v>
+        <v>0.01004669774163585</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006643594336321717</v>
+        <v>0.003510122628458535</v>
       </c>
     </row>
     <row r="6">
@@ -759,16 +760,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-7.717382896603793</v>
+        <v>-0.5704258766470407</v>
       </c>
       <c r="D6" t="n">
-        <v>4.296296477094853</v>
+        <v>0.7633932346542655</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7173814187628933</v>
+        <v>0.1292353859883709</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3535560269315549</v>
+        <v>0.06282207954449587</v>
       </c>
     </row>
     <row r="7">
@@ -783,16 +784,207 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9773886650431113</v>
+        <v>0.979480093193948</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003865209262172529</v>
+        <v>0.002363311441781221</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002080341725822704</v>
+        <v>0.001887921187316615</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0003556161598802079</v>
+        <v>0.0002174349905843939</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Neurons</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Best_R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Train_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>model_264_Ld0.7_Lp0.3_r0.01_seed4</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[264]</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9282310604023589</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Train_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>model_264_128_Ld0.7_Lp0.3_r0.01_seed3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[264, 128]</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.5416384546839299</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Val</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>model_264_Ld0.7_Lp0.3_r0.01_seed0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[264]</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.954110005760336</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Test_1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>model_264_Ld0.7_Lp0.3_r0.01_seed4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[264]</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9530862262732048</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Test_2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>model_264_128_Ld0.7_Lp0.3_r0.01_seed3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[264, 128]</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.4812604678356515</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Test_3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>model_264_128_64_Ld0.7_Lp0.3_r0.9_seed1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[264, 128, 64]</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9821418184339715</v>
       </c>
     </row>
   </sheetData>
